--- a/02_DIA_inicio_2026_analisis_assets/rbd_9701_liceo-polivalente-olof-palme_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9701_liceo-polivalente-olof-palme_nt1_rubricas.xlsx
@@ -1608,13 +1608,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B68EE1-35C3-4E44-9852-24083B996814}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B76D9557-299A-4305-972E-7C63998420F6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23CBC5DD-A865-40DA-9F65-60EB4B177C48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6976371A-F252-4632-9B2A-62F62A4484F6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A5712B-A564-46B9-A908-30A8C0F6CF13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C97632A-E4F4-4AB8-839D-550C1AF6F1CA}"/>
 </file>